--- a/cloudflare-deploy/public/library/admin/admin-en.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-en.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1835,6 +1835,114 @@
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>Listen slowly and repeat clearly to nail the four tones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>📢</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Notice Studio (Poster + Popup)</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Go to the admin menu Notification Center → 📢 Notice Studio. → In the ①Create tab, design a poster with text, images, and video (resize · save on server · reuse). → Press ‘📢 Publish as popup’ on the finished poster to auto-switch to the ②Publish·Popup tab. → In the publish tab, set the display period / stop and publish it as a student-app popup.</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>Promoting an event takes just one flow: ‘Create → Publish as popup’ right away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Command the AI Operations Assistant</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Type a command in the top search bar or speak with the 🎤 mic. → e.g. “Take me to teacher Kim Minji's schedule” → auto-finds that teacher in the weekly schedule and opens it. → e.g. “Open auto-scheduling,” “Go to settlement” to navigate menus. → Press ‘Go now →’ on the AI response card to move to that screen.</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>When you can't recall a menu name, just say what you want to do — it finds its way there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>📔</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Student Voice-Diary Monitor</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Open the 📔 Voice Diary (monitor) card in the admin menu. → Enter the student UID, pick the month to look up, and press ‘Search’. → Open an entry from the list to see the transcript · correction · encouragement · score.</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>‘Nothing shows up’ usually just means that student hasn't left a diary yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>🤖</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Teacher AI-Coaching Review (Ops)</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Go to admin 🧲 Retention Center → 💼 Teacher Coaching tab. → In the ‘🤖 Per-class AI coaching (recent)’ section, review each teacher's latest coaching. → Use each card's quality score · talk ratio · improvement point to plan coaching and training.</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>For teachers whose quality score stays low, coach them together with the teacher training manual.</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F229"/>
+  <dimension ref="A1:F276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4382,44 +4490,583 @@
       <c r="E229" s="33" t="n"/>
       <c r="F229" s="33" t="n"/>
     </row>
+    <row r="231" ht="26" customHeight="1">
+      <c r="A231" s="21" t="inlineStr">
+        <is>
+          <t>22  📢 Notice Studio (Poster + Popup)  —  Design notice/event posters and push them as app popups</t>
+        </is>
+      </c>
+      <c r="B231" s="22" t="n"/>
+      <c r="C231" s="22" t="n"/>
+      <c r="D231" s="22" t="n"/>
+      <c r="E231" s="22" t="n"/>
+      <c r="F231" s="22" t="n"/>
+    </row>
+    <row r="232" ht="42" customHeight="1">
+      <c r="A232" s="23" t="inlineStr">
+        <is>
+          <t>📖 This merges the old ‘Poster Maker’ and ‘Popup Notice’ tools into one place. In the ①Create tab you design a notice/event poster, then hand it straight to the ②Publish·Popup tab to show it as a popup in your academy's student app.</t>
+        </is>
+      </c>
+      <c r="B232" s="24" t="n"/>
+      <c r="C232" s="24" t="n"/>
+      <c r="D232" s="24" t="n"/>
+      <c r="E232" s="24" t="n"/>
+      <c r="F232" s="24" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B233" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="30" customHeight="1">
+      <c r="A234" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B234" s="28" t="inlineStr">
+        <is>
+          <t>Go to the admin menu Notification Center → 📢 Notice Studio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="30" customHeight="1">
+      <c r="A235" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B235" s="28" t="inlineStr">
+        <is>
+          <t>In the ①Create tab, design a poster with text, images, and video (resize · save on server · reuse).</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="30" customHeight="1">
+      <c r="A236" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B236" s="28" t="inlineStr">
+        <is>
+          <t>Press ‘📢 Publish as popup’ on the finished poster to auto-switch to the ②Publish·Popup tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="30" customHeight="1">
+      <c r="A237" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B237" s="28" t="inlineStr">
+        <is>
+          <t>In the publish tab, set the display period / stop and publish it as a student-app popup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="24" customHeight="1">
+      <c r="A238" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B238" s="30" t="inlineStr">
+        <is>
+          <t>Poster creation and popup publishing flow through one screen, two tabs — no more confusion.</t>
+        </is>
+      </c>
+      <c r="C238" s="31" t="n"/>
+      <c r="D238" s="31" t="n"/>
+      <c r="E238" s="31" t="n"/>
+      <c r="F238" s="31" t="n"/>
+    </row>
+    <row r="239" ht="24" customHeight="1">
+      <c r="A239" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B239" s="30" t="inlineStr">
+        <is>
+          <t>Posters you make can be saved and reused.</t>
+        </is>
+      </c>
+      <c r="C239" s="31" t="n"/>
+      <c r="D239" s="31" t="n"/>
+      <c r="E239" s="31" t="n"/>
+      <c r="F239" s="31" t="n"/>
+    </row>
+    <row r="240" ht="24" customHeight="1">
+      <c r="A240" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B240" s="30" t="inlineStr">
+        <is>
+          <t>Whichever route you enter from — AI assistant or sidebar search — the correct tab opens.</t>
+        </is>
+      </c>
+      <c r="C240" s="31" t="n"/>
+      <c r="D240" s="31" t="n"/>
+      <c r="E240" s="31" t="n"/>
+      <c r="F240" s="31" t="n"/>
+    </row>
+    <row r="241" ht="26" customHeight="1">
+      <c r="A241" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Existing posters/popups are preserved (it was only merged, nothing was deleted).</t>
+        </is>
+      </c>
+      <c r="B241" s="35" t="n"/>
+      <c r="C241" s="35" t="n"/>
+      <c r="D241" s="35" t="n"/>
+      <c r="E241" s="35" t="n"/>
+      <c r="F241" s="35" t="n"/>
+    </row>
+    <row r="242" ht="30" customHeight="1">
+      <c r="A242" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Promoting an event takes just one flow: ‘Create → Publish as popup’ right away.</t>
+        </is>
+      </c>
+      <c r="B242" s="33" t="n"/>
+      <c r="C242" s="33" t="n"/>
+      <c r="D242" s="33" t="n"/>
+      <c r="E242" s="33" t="n"/>
+      <c r="F242" s="33" t="n"/>
+    </row>
+    <row r="244" ht="26" customHeight="1">
+      <c r="A244" s="21" t="inlineStr">
+        <is>
+          <t>23  🤖 Command the AI Operations Assistant  —  Navigate with one phrase: “Take me to ○○”</t>
+        </is>
+      </c>
+      <c r="B244" s="22" t="n"/>
+      <c r="C244" s="22" t="n"/>
+      <c r="D244" s="22" t="n"/>
+      <c r="E244" s="22" t="n"/>
+      <c r="F244" s="22" t="n"/>
+    </row>
+    <row r="245" ht="42" customHeight="1">
+      <c r="A245" s="23" t="inlineStr">
+        <is>
+          <t>📖 Type what you want to do into the top search bar (or the bottom-right AI assistant) in plain language, and the AI understands and jumps straight to that screen. It now reliably follows navigation commands like ‘Take me to teacher ○○'s schedule’ or ‘Open auto-scheduling’.</t>
+        </is>
+      </c>
+      <c r="B245" s="24" t="n"/>
+      <c r="C245" s="24" t="n"/>
+      <c r="D245" s="24" t="n"/>
+      <c r="E245" s="24" t="n"/>
+      <c r="F245" s="24" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B246" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="30" customHeight="1">
+      <c r="A247" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B247" s="28" t="inlineStr">
+        <is>
+          <t>Type a command in the top search bar or speak with the 🎤 mic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="30" customHeight="1">
+      <c r="A248" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B248" s="28" t="inlineStr">
+        <is>
+          <t>e.g. “Take me to teacher Kim Minji's schedule” → auto-finds that teacher in the weekly schedule and opens it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="30" customHeight="1">
+      <c r="A249" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B249" s="28" t="inlineStr">
+        <is>
+          <t>e.g. “Open auto-scheduling,” “Go to settlement” to navigate menus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="30" customHeight="1">
+      <c r="A250" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B250" s="28" t="inlineStr">
+        <is>
+          <t>Press ‘Go now →’ on the AI response card to move to that screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="24" customHeight="1">
+      <c r="A251" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B251" s="30" t="inlineStr">
+        <is>
+          <t>Navigation commands actually navigate — far fewer ‘explain only, do nothing’ replies.</t>
+        </is>
+      </c>
+      <c r="C251" s="31" t="n"/>
+      <c r="D251" s="31" t="n"/>
+      <c r="E251" s="31" t="n"/>
+      <c r="F251" s="31" t="n"/>
+    </row>
+    <row r="252" ht="24" customHeight="1">
+      <c r="A252" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B252" s="30" t="inlineStr">
+        <is>
+          <t>Searching a schedule by teacher name auto-fills the search box + filters + scrolls.</t>
+        </is>
+      </c>
+      <c r="C252" s="31" t="n"/>
+      <c r="D252" s="31" t="n"/>
+      <c r="E252" s="31" t="n"/>
+      <c r="F252" s="31" t="n"/>
+    </row>
+    <row r="253" ht="24" customHeight="1">
+      <c r="A253" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B253" s="30" t="inlineStr">
+        <is>
+          <t>For data/statistics questions it also helps with card-style answers.</t>
+        </is>
+      </c>
+      <c r="C253" s="31" t="n"/>
+      <c r="D253" s="31" t="n"/>
+      <c r="E253" s="31" t="n"/>
+      <c r="F253" s="31" t="n"/>
+    </row>
+    <row r="254" ht="26" customHeight="1">
+      <c r="A254" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Commands that actually change things — ‘register · send · modify’ — ask for one more confirmation (a safety guard).</t>
+        </is>
+      </c>
+      <c r="B254" s="35" t="n"/>
+      <c r="C254" s="35" t="n"/>
+      <c r="D254" s="35" t="n"/>
+      <c r="E254" s="35" t="n"/>
+      <c r="F254" s="35" t="n"/>
+    </row>
+    <row r="255" ht="30" customHeight="1">
+      <c r="A255" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · When you can't recall a menu name, just say what you want to do — it finds its way there.</t>
+        </is>
+      </c>
+      <c r="B255" s="33" t="n"/>
+      <c r="C255" s="33" t="n"/>
+      <c r="D255" s="33" t="n"/>
+      <c r="E255" s="33" t="n"/>
+      <c r="F255" s="33" t="n"/>
+    </row>
+    <row r="257" ht="26" customHeight="1">
+      <c r="A257" s="21" t="inlineStr">
+        <is>
+          <t>24  📔 Student Voice-Diary Monitor  —  View each student's English diary · AI correction · score</t>
+        </is>
+      </c>
+      <c r="B257" s="22" t="n"/>
+      <c r="C257" s="22" t="n"/>
+      <c r="D257" s="22" t="n"/>
+      <c r="E257" s="22" t="n"/>
+      <c r="F257" s="22" t="n"/>
+    </row>
+    <row r="258" ht="42" customHeight="1">
+      <c r="A258" s="23" t="inlineStr">
+        <is>
+          <t>📖 View the AI voice diaries students leave, right from the admin screen. Per student, check the transcript · AI correction · encouragement · score by month to encourage consistent writers and gauge their learning.</t>
+        </is>
+      </c>
+      <c r="B258" s="24" t="n"/>
+      <c r="C258" s="24" t="n"/>
+      <c r="D258" s="24" t="n"/>
+      <c r="E258" s="24" t="n"/>
+      <c r="F258" s="24" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B259" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B260" s="28" t="inlineStr">
+        <is>
+          <t>Open the 📔 Voice Diary (monitor) card in the admin menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="30" customHeight="1">
+      <c r="A261" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B261" s="28" t="inlineStr">
+        <is>
+          <t>Enter the student UID, pick the month to look up, and press ‘Search’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="30" customHeight="1">
+      <c r="A262" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B262" s="28" t="inlineStr">
+        <is>
+          <t>Open an entry from the list to see the transcript · correction · encouragement · score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="24" customHeight="1">
+      <c r="A263" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B263" s="30" t="inlineStr">
+        <is>
+          <t>It only shows up once a student actually writes a diary (the entry point is the 📔 card on the student home).</t>
+        </is>
+      </c>
+      <c r="C263" s="31" t="n"/>
+      <c r="D263" s="31" t="n"/>
+      <c r="E263" s="31" t="n"/>
+      <c r="F263" s="31" t="n"/>
+    </row>
+    <row r="264" ht="24" customHeight="1">
+      <c r="A264" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B264" s="30" t="inlineStr">
+        <is>
+          <t>Find consistent writers and connect them to praise/rewards to lock in the habit.</t>
+        </is>
+      </c>
+      <c r="C264" s="31" t="n"/>
+      <c r="D264" s="31" t="n"/>
+      <c r="E264" s="31" t="n"/>
+      <c r="F264" s="31" t="n"/>
+    </row>
+    <row r="265" ht="30" customHeight="1">
+      <c r="A265" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · ‘Nothing shows up’ usually just means that student hasn't left a diary yet.</t>
+        </is>
+      </c>
+      <c r="B265" s="33" t="n"/>
+      <c r="C265" s="33" t="n"/>
+      <c r="D265" s="33" t="n"/>
+      <c r="E265" s="33" t="n"/>
+      <c r="F265" s="33" t="n"/>
+    </row>
+    <row r="267" ht="26" customHeight="1">
+      <c r="A267" s="21" t="inlineStr">
+        <is>
+          <t>25  🤖 Teacher AI-Coaching Review (Ops)  —  Collected per-class AI coaching · quality scores</t>
+        </is>
+      </c>
+      <c r="B267" s="22" t="n"/>
+      <c r="C267" s="22" t="n"/>
+      <c r="D267" s="22" t="n"/>
+      <c r="E267" s="22" t="n"/>
+      <c r="F267" s="22" t="n"/>
+    </row>
+    <row r="268" ht="42" customHeight="1">
+      <c r="A268" s="23" t="inlineStr">
+        <is>
+          <t>📖 After every class, the AI leaves the teacher a coaching card (strengths · areas to improve · a class-quality score). From the admin screen you can see these gathered by most-recent. Use it as a growth-support / coaching-quality tool — not surveillance.</t>
+        </is>
+      </c>
+      <c r="B268" s="24" t="n"/>
+      <c r="C268" s="24" t="n"/>
+      <c r="D268" s="24" t="n"/>
+      <c r="E268" s="24" t="n"/>
+      <c r="F268" s="24" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B269" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="30" customHeight="1">
+      <c r="A270" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B270" s="28" t="inlineStr">
+        <is>
+          <t>Go to admin 🧲 Retention Center → 💼 Teacher Coaching tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="30" customHeight="1">
+      <c r="A271" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B271" s="28" t="inlineStr">
+        <is>
+          <t>In the ‘🤖 Per-class AI coaching (recent)’ section, review each teacher's latest coaching.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="30" customHeight="1">
+      <c r="A272" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B272" s="28" t="inlineStr">
+        <is>
+          <t>Use each card's quality score · talk ratio · improvement point to plan coaching and training.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="24" customHeight="1">
+      <c r="A273" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B273" s="30" t="inlineStr">
+        <is>
+          <t>See every teacher's recent coaching at a glance.</t>
+        </is>
+      </c>
+      <c r="C273" s="31" t="n"/>
+      <c r="D273" s="31" t="n"/>
+      <c r="E273" s="31" t="n"/>
+      <c r="F273" s="31" t="n"/>
+    </row>
+    <row r="274" ht="24" customHeight="1">
+      <c r="A274" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B274" s="30" t="inlineStr">
+        <is>
+          <t>Admins get a monthly rollup focus, so it's low-pressure.</t>
+        </is>
+      </c>
+      <c r="C274" s="31" t="n"/>
+      <c r="D274" s="31" t="n"/>
+      <c r="E274" s="31" t="n"/>
+      <c r="F274" s="31" t="n"/>
+    </row>
+    <row r="275" ht="26" customHeight="1">
+      <c r="A275" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Coaching text is for a teacher's personal growth. We recommend using it as a support tool, not for evaluation/discipline.</t>
+        </is>
+      </c>
+      <c r="B275" s="35" t="n"/>
+      <c r="C275" s="35" t="n"/>
+      <c r="D275" s="35" t="n"/>
+      <c r="E275" s="35" t="n"/>
+      <c r="F275" s="35" t="n"/>
+    </row>
+    <row r="276" ht="30" customHeight="1">
+      <c r="A276" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · For teachers whose quality score stays low, coach them together with the teacher training manual.</t>
+        </is>
+      </c>
+      <c r="B276" s="33" t="n"/>
+      <c r="C276" s="33" t="n"/>
+      <c r="D276" s="33" t="n"/>
+      <c r="E276" s="33" t="n"/>
+      <c r="F276" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="208">
+  <mergeCells count="251">
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B252:F252"/>
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="A189:F189"/>
+    <mergeCell ref="B261:F261"/>
     <mergeCell ref="A158:F158"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B184:F184"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B236:F236"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B180:F180"/>
     <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B238:F238"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B253:F253"/>
     <mergeCell ref="A159:F159"/>
     <mergeCell ref="B170:F170"/>
     <mergeCell ref="A200:F200"/>
+    <mergeCell ref="B250:F250"/>
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:F53"/>
+    <mergeCell ref="A265:F265"/>
+    <mergeCell ref="B234:F234"/>
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B270:F270"/>
     <mergeCell ref="B174:F174"/>
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B186:F186"/>
+    <mergeCell ref="A258:F258"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="B118:F118"/>
     <mergeCell ref="B143:F143"/>
+    <mergeCell ref="A257:F257"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A60:F60"/>
@@ -4428,15 +5075,18 @@
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="B213:F213"/>
+    <mergeCell ref="A241:F241"/>
     <mergeCell ref="B160:F160"/>
     <mergeCell ref="A124:F124"/>
     <mergeCell ref="B144:F144"/>
+    <mergeCell ref="B233:F233"/>
     <mergeCell ref="B227:F227"/>
     <mergeCell ref="B224:F224"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B72:F72"/>
     <mergeCell ref="B185:F185"/>
     <mergeCell ref="B134:F134"/>
+    <mergeCell ref="A267:F267"/>
     <mergeCell ref="A149:F149"/>
     <mergeCell ref="B121:F121"/>
     <mergeCell ref="A101:F101"/>
@@ -4448,6 +5098,7 @@
     <mergeCell ref="B111:F111"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B98:F98"/>
+    <mergeCell ref="A254:F254"/>
     <mergeCell ref="A135:F135"/>
     <mergeCell ref="B107:F107"/>
     <mergeCell ref="B8:F8"/>
@@ -4465,24 +5116,30 @@
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A176:F176"/>
+    <mergeCell ref="A232:F232"/>
     <mergeCell ref="A114:F114"/>
+    <mergeCell ref="B269:F269"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B239:F239"/>
     <mergeCell ref="B153:F153"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A178:F178"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B251:F251"/>
     <mergeCell ref="B76:F76"/>
     <mergeCell ref="B204:F204"/>
     <mergeCell ref="B216:F216"/>
     <mergeCell ref="B85:F85"/>
     <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B271:F271"/>
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="A137:F137"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="B62:F62"/>
+    <mergeCell ref="A268:F268"/>
     <mergeCell ref="A217:F217"/>
     <mergeCell ref="B141:F141"/>
     <mergeCell ref="B193:F193"/>
@@ -4491,19 +5148,28 @@
     <mergeCell ref="B202:F202"/>
     <mergeCell ref="A145:F145"/>
     <mergeCell ref="B215:F215"/>
+    <mergeCell ref="B273:F273"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A210:F210"/>
     <mergeCell ref="A179:F179"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A242:F242"/>
+    <mergeCell ref="B263:F263"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B272:F272"/>
     <mergeCell ref="B161:F161"/>
     <mergeCell ref="A116:F116"/>
+    <mergeCell ref="B259:F259"/>
+    <mergeCell ref="A244:F244"/>
     <mergeCell ref="B181:F181"/>
     <mergeCell ref="B225:F225"/>
+    <mergeCell ref="A231:F231"/>
+    <mergeCell ref="B274:F274"/>
     <mergeCell ref="B191:F191"/>
     <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B249:F249"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A68:F68"/>
@@ -4512,6 +5178,9 @@
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A83:F83"/>
     <mergeCell ref="B226:F226"/>
+    <mergeCell ref="A245:F245"/>
+    <mergeCell ref="A276:F276"/>
+    <mergeCell ref="B260:F260"/>
     <mergeCell ref="A166:F166"/>
     <mergeCell ref="B183:F183"/>
     <mergeCell ref="B65:F65"/>
@@ -4540,6 +5209,7 @@
     <mergeCell ref="B221:F221"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="B100:F100"/>
+    <mergeCell ref="A255:F255"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="B165:F165"/>
@@ -4548,16 +5218,22 @@
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B140:F140"/>
     <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B264:F264"/>
     <mergeCell ref="A104:F104"/>
+    <mergeCell ref="B247:F247"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="B248:F248"/>
+    <mergeCell ref="B262:F262"/>
     <mergeCell ref="A219:F219"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="B151:F151"/>
+    <mergeCell ref="B235:F235"/>
+    <mergeCell ref="B240:F240"/>
     <mergeCell ref="B67:F67"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="A4:F4"/>
@@ -4574,9 +5250,11 @@
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B205:F205"/>
     <mergeCell ref="A220:F220"/>
+    <mergeCell ref="B246:F246"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="B211:F211"/>
+    <mergeCell ref="A275:F275"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B95:F95"/>
@@ -4592,6 +5270,7 @@
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="A25:F25"/>
+    <mergeCell ref="B237:F237"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cloudflare-deploy/public/library/admin/admin-en.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-en.xlsx
@@ -1130,7 +1130,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>🌐 test.mangoi.co.kr    📞 1588-0000    ✉ support@mangoi.co.kr</t>
+          <t>🌐 www.mangoi.co.kr    📞 1644-0561    ✉ support@mangoi.co.kr</t>
         </is>
       </c>
     </row>

--- a/cloudflare-deploy/public/library/admin/admin-en.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-en.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1943,6 +1943,141 @@
       <c r="E28" s="15" t="inlineStr">
         <is>
           <t>For teachers whose quality score stays low, coach them together with the teacher training manual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>📱</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>QR Attendance Check-in</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>Open the QR Attendance card in the admin menu and generate your academy's QR code. → Print the QR and post it at the entrance or front desk. → Students scan with their phone camera and check in on the check-in screen. → Watch today's arrivals and times live on the dashboard's attendance view.</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>Stand a tablet at the desk during arrival hours so students can scan without queuing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>📞</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Consultation Booking Management</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Open the Consultation Booking card in the admin menu. → Register a new booking (name, contact, preferred time) or review incoming ones. → After the consult, set the status to done and leave a note. → Carry it forward: consult → level test → enrollment.</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>A quick follow-up call the day after a consult noticeably lifts enrollment conversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Friend-Referral Rewards</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Open the Referral Rewards card in the admin menu. → Review the list of referrer · referred friend · enrollment status. → For qualifying cases, process the reward payout (points, gift vouchers, etc.).</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>Pair it with a 'refer a friend' event before each semester and watch inquiries jump.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>🗓️</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Approving Postpone/Change Requests</t>
+        </is>
+      </c>
+      <c r="D32" s="14" t="inlineStr">
+        <is>
+          <t>Open the Class Postpone/Change Requests card in the admin menu. → Review each pending request's teacher · class · reason. → Press Approve or Decline — the result flows to the schedule and the teacher.</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>Clearing pending requests every morning prevents same-day confusion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>💬</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Share Library Links via KakaoTalk</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>In the admin Library, press 💬 Copy KakaoTalk link next to the file. → Paste it into the KakaoTalk chat room. → Recipients tap the link to watch or download in original quality.</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>In a parents' group chat, one video-guide link does all the explaining.</t>
         </is>
       </c>
     </row>
@@ -1960,7 +2095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F276"/>
+  <dimension ref="A1:F330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5018,8 +5153,602 @@
       <c r="E276" s="33" t="n"/>
       <c r="F276" s="33" t="n"/>
     </row>
+    <row r="278" ht="26" customHeight="1">
+      <c r="A278" s="21" t="inlineStr">
+        <is>
+          <t>26  📱 QR Attendance Check-in  —  One scan and attendance is done</t>
+        </is>
+      </c>
+      <c r="B278" s="22" t="n"/>
+      <c r="C278" s="22" t="n"/>
+      <c r="D278" s="22" t="n"/>
+      <c r="E278" s="22" t="n"/>
+      <c r="F278" s="22" t="n"/>
+    </row>
+    <row r="279" ht="42" customHeight="1">
+      <c r="A279" s="23" t="inlineStr">
+        <is>
+          <t>📖 Post an attendance QR code at the entrance, and the moment a student scans it with their phone, attendance is recorded automatically. The admin dashboard shows today's attendance in real time — no more paper rosters.</t>
+        </is>
+      </c>
+      <c r="B279" s="24" t="n"/>
+      <c r="C279" s="24" t="n"/>
+      <c r="D279" s="24" t="n"/>
+      <c r="E279" s="24" t="n"/>
+      <c r="F279" s="24" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B280" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="30" customHeight="1">
+      <c r="A281" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B281" s="28" t="inlineStr">
+        <is>
+          <t>Open the QR Attendance card in the admin menu and generate your academy's QR code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="30" customHeight="1">
+      <c r="A282" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B282" s="28" t="inlineStr">
+        <is>
+          <t>Print the QR and post it at the entrance or front desk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="30" customHeight="1">
+      <c r="A283" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B283" s="28" t="inlineStr">
+        <is>
+          <t>Students scan with their phone camera and check in on the check-in screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="30" customHeight="1">
+      <c r="A284" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B284" s="28" t="inlineStr">
+        <is>
+          <t>Watch today's arrivals and times live on the dashboard's attendance view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="24" customHeight="1">
+      <c r="A285" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B285" s="30" t="inlineStr">
+        <is>
+          <t>Arrival times are recorded automatically — fast and accurate.</t>
+        </is>
+      </c>
+      <c r="C285" s="31" t="n"/>
+      <c r="D285" s="31" t="n"/>
+      <c r="E285" s="31" t="n"/>
+      <c r="F285" s="31" t="n"/>
+    </row>
+    <row r="286" ht="24" customHeight="1">
+      <c r="A286" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B286" s="30" t="inlineStr">
+        <is>
+          <t>Attendance data flows into student management and reports.</t>
+        </is>
+      </c>
+      <c r="C286" s="31" t="n"/>
+      <c r="D286" s="31" t="n"/>
+      <c r="E286" s="31" t="n"/>
+      <c r="F286" s="31" t="n"/>
+    </row>
+    <row r="287" ht="26" customHeight="1">
+      <c r="A287" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · The QR code is unique to your academy. Keep it from being shared outside.</t>
+        </is>
+      </c>
+      <c r="B287" s="35" t="n"/>
+      <c r="C287" s="35" t="n"/>
+      <c r="D287" s="35" t="n"/>
+      <c r="E287" s="35" t="n"/>
+      <c r="F287" s="35" t="n"/>
+    </row>
+    <row r="288" ht="30" customHeight="1">
+      <c r="A288" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Stand a tablet at the desk during arrival hours so students can scan without queuing.</t>
+        </is>
+      </c>
+      <c r="B288" s="33" t="n"/>
+      <c r="C288" s="33" t="n"/>
+      <c r="D288" s="33" t="n"/>
+      <c r="E288" s="33" t="n"/>
+      <c r="F288" s="33" t="n"/>
+    </row>
+    <row r="290" ht="26" customHeight="1">
+      <c r="A290" s="21" t="inlineStr">
+        <is>
+          <t>27  📞 Consultation Booking Management  —  From new inquiries to scheduled consults</t>
+        </is>
+      </c>
+      <c r="B290" s="22" t="n"/>
+      <c r="C290" s="22" t="n"/>
+      <c r="D290" s="22" t="n"/>
+      <c r="E290" s="22" t="n"/>
+      <c r="F290" s="22" t="n"/>
+    </row>
+    <row r="291" ht="42" customHeight="1">
+      <c r="A291" s="23" t="inlineStr">
+        <is>
+          <t>📖 Take consultation bookings from parents and prospects and manage them on one screen. Track each booking's schedule and status (pending/done) and carry the consult onward toward enrollment.</t>
+        </is>
+      </c>
+      <c r="B291" s="24" t="n"/>
+      <c r="C291" s="24" t="n"/>
+      <c r="D291" s="24" t="n"/>
+      <c r="E291" s="24" t="n"/>
+      <c r="F291" s="24" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B292" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="30" customHeight="1">
+      <c r="A293" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B293" s="28" t="inlineStr">
+        <is>
+          <t>Open the Consultation Booking card in the admin menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="30" customHeight="1">
+      <c r="A294" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B294" s="28" t="inlineStr">
+        <is>
+          <t>Register a new booking (name, contact, preferred time) or review incoming ones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="30" customHeight="1">
+      <c r="A295" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B295" s="28" t="inlineStr">
+        <is>
+          <t>After the consult, set the status to done and leave a note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="30" customHeight="1">
+      <c r="A296" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B296" s="28" t="inlineStr">
+        <is>
+          <t>Carry it forward: consult → level test → enrollment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="24" customHeight="1">
+      <c r="A297" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B297" s="30" t="inlineStr">
+        <is>
+          <t>Bookings live in one place, so no consult slips through.</t>
+        </is>
+      </c>
+      <c r="C297" s="31" t="n"/>
+      <c r="D297" s="31" t="n"/>
+      <c r="E297" s="31" t="n"/>
+      <c r="F297" s="31" t="n"/>
+    </row>
+    <row r="298" ht="24" customHeight="1">
+      <c r="A298" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B298" s="30" t="inlineStr">
+        <is>
+          <t>Consult history makes repeat inquiries easy to handle.</t>
+        </is>
+      </c>
+      <c r="C298" s="31" t="n"/>
+      <c r="D298" s="31" t="n"/>
+      <c r="E298" s="31" t="n"/>
+      <c r="F298" s="31" t="n"/>
+    </row>
+    <row r="299" ht="30" customHeight="1">
+      <c r="A299" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · A quick follow-up call the day after a consult noticeably lifts enrollment conversion.</t>
+        </is>
+      </c>
+      <c r="B299" s="33" t="n"/>
+      <c r="C299" s="33" t="n"/>
+      <c r="D299" s="33" t="n"/>
+      <c r="E299" s="33" t="n"/>
+      <c r="F299" s="33" t="n"/>
+    </row>
+    <row r="301" ht="26" customHeight="1">
+      <c r="A301" s="21" t="inlineStr">
+        <is>
+          <t>28  🎁 Friend-Referral Rewards  —  Track referrals · pay out rewards</t>
+        </is>
+      </c>
+      <c r="B301" s="22" t="n"/>
+      <c r="C301" s="22" t="n"/>
+      <c r="D301" s="22" t="n"/>
+      <c r="E301" s="22" t="n"/>
+      <c r="F301" s="22" t="n"/>
+    </row>
+    <row r="302" ht="42" customHeight="1">
+      <c r="A302" s="23" t="inlineStr">
+        <is>
+          <t>📖 See the referral status of enrolled students bringing friends, and process reward payouts. Who referred whom, and whether the reward was paid — all on one screen, turning word-of-mouth into a system.</t>
+        </is>
+      </c>
+      <c r="B302" s="24" t="n"/>
+      <c r="C302" s="24" t="n"/>
+      <c r="D302" s="24" t="n"/>
+      <c r="E302" s="24" t="n"/>
+      <c r="F302" s="24" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B303" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="30" customHeight="1">
+      <c r="A304" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B304" s="28" t="inlineStr">
+        <is>
+          <t>Open the Referral Rewards card in the admin menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="30" customHeight="1">
+      <c r="A305" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B305" s="28" t="inlineStr">
+        <is>
+          <t>Review the list of referrer · referred friend · enrollment status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="30" customHeight="1">
+      <c r="A306" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B306" s="28" t="inlineStr">
+        <is>
+          <t>For qualifying cases, process the reward payout (points, gift vouchers, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="24" customHeight="1">
+      <c r="A307" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B307" s="30" t="inlineStr">
+        <is>
+          <t>Referral history is kept as data — transparent, no disputes.</t>
+        </is>
+      </c>
+      <c r="C307" s="31" t="n"/>
+      <c r="D307" s="31" t="n"/>
+      <c r="E307" s="31" t="n"/>
+      <c r="F307" s="31" t="n"/>
+    </row>
+    <row r="308" ht="24" customHeight="1">
+      <c r="A308" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B308" s="30" t="inlineStr">
+        <is>
+          <t>Linking rewards to student points and the shop multiplies the effect.</t>
+        </is>
+      </c>
+      <c r="C308" s="31" t="n"/>
+      <c r="D308" s="31" t="n"/>
+      <c r="E308" s="31" t="n"/>
+      <c r="F308" s="31" t="n"/>
+    </row>
+    <row r="309" ht="30" customHeight="1">
+      <c r="A309" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Pair it with a 'refer a friend' event before each semester and watch inquiries jump.</t>
+        </is>
+      </c>
+      <c r="B309" s="33" t="n"/>
+      <c r="C309" s="33" t="n"/>
+      <c r="D309" s="33" t="n"/>
+      <c r="E309" s="33" t="n"/>
+      <c r="F309" s="33" t="n"/>
+    </row>
+    <row r="311" ht="26" customHeight="1">
+      <c r="A311" s="21" t="inlineStr">
+        <is>
+          <t>29  🗓️ Approving Postpone/Change Requests  —  Review and approve teacher-submitted requests</t>
+        </is>
+      </c>
+      <c r="B311" s="22" t="n"/>
+      <c r="C311" s="22" t="n"/>
+      <c r="D311" s="22" t="n"/>
+      <c r="E311" s="22" t="n"/>
+      <c r="F311" s="22" t="n"/>
+    </row>
+    <row r="312" ht="42" customHeight="1">
+      <c r="A312" s="23" t="inlineStr">
+        <is>
+          <t>📖 Class postpone and time-change requests submitted by teachers gather on the admin screen in real time. Check the reason and approve or decline — the schedule updates immediately, replacing phone-and-messenger juggling with one screen.</t>
+        </is>
+      </c>
+      <c r="B312" s="24" t="n"/>
+      <c r="C312" s="24" t="n"/>
+      <c r="D312" s="24" t="n"/>
+      <c r="E312" s="24" t="n"/>
+      <c r="F312" s="24" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B313" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="30" customHeight="1">
+      <c r="A314" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B314" s="28" t="inlineStr">
+        <is>
+          <t>Open the Class Postpone/Change Requests card in the admin menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="30" customHeight="1">
+      <c r="A315" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B315" s="28" t="inlineStr">
+        <is>
+          <t>Review each pending request's teacher · class · reason.</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="30" customHeight="1">
+      <c r="A316" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B316" s="28" t="inlineStr">
+        <is>
+          <t>Press Approve or Decline — the result flows to the schedule and the teacher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="24" customHeight="1">
+      <c r="A317" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B317" s="30" t="inlineStr">
+        <is>
+          <t>Request and decision history is kept, so everything stays transparent.</t>
+        </is>
+      </c>
+      <c r="C317" s="31" t="n"/>
+      <c r="D317" s="31" t="n"/>
+      <c r="E317" s="31" t="n"/>
+      <c r="F317" s="31" t="n"/>
+    </row>
+    <row r="318" ht="24" customHeight="1">
+      <c r="A318" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B318" s="30" t="inlineStr">
+        <is>
+          <t>For changes parents should know about, follow approval with a notification.</t>
+        </is>
+      </c>
+      <c r="C318" s="31" t="n"/>
+      <c r="D318" s="31" t="n"/>
+      <c r="E318" s="31" t="n"/>
+      <c r="F318" s="31" t="n"/>
+    </row>
+    <row r="319" ht="30" customHeight="1">
+      <c r="A319" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Clearing pending requests every morning prevents same-day confusion.</t>
+        </is>
+      </c>
+      <c r="B319" s="33" t="n"/>
+      <c r="C319" s="33" t="n"/>
+      <c r="D319" s="33" t="n"/>
+      <c r="E319" s="33" t="n"/>
+      <c r="F319" s="33" t="n"/>
+    </row>
+    <row r="321" ht="26" customHeight="1">
+      <c r="A321" s="21" t="inlineStr">
+        <is>
+          <t>30  💬 Share Library Links via KakaoTalk  —  Send videos &amp; docs in original quality</t>
+        </is>
+      </c>
+      <c r="B321" s="22" t="n"/>
+      <c r="C321" s="22" t="n"/>
+      <c r="D321" s="22" t="n"/>
+      <c r="E321" s="22" t="n"/>
+      <c r="F321" s="22" t="n"/>
+    </row>
+    <row r="322" ht="42" customHeight="1">
+      <c r="A322" s="23" t="inlineStr">
+        <is>
+          <t>📖 Every guide and video in the library now has a '💬 Copy KakaoTalk link' button. Attaching a file to KakaoTalk crushes the quality, but sending a link plays the original as-is. One tap copies the link — guiding parents and teachers gets much easier.</t>
+        </is>
+      </c>
+      <c r="B322" s="24" t="n"/>
+      <c r="C322" s="24" t="n"/>
+      <c r="D322" s="24" t="n"/>
+      <c r="E322" s="24" t="n"/>
+      <c r="F322" s="24" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B323" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="30" customHeight="1">
+      <c r="A324" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B324" s="28" t="inlineStr">
+        <is>
+          <t>In the admin Library, press 💬 Copy KakaoTalk link next to the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="30" customHeight="1">
+      <c r="A325" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B325" s="28" t="inlineStr">
+        <is>
+          <t>Paste it into the KakaoTalk chat room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="30" customHeight="1">
+      <c r="A326" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B326" s="28" t="inlineStr">
+        <is>
+          <t>Recipients tap the link to watch or download in original quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="24" customHeight="1">
+      <c r="A327" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B327" s="30" t="inlineStr">
+        <is>
+          <t>For videos, link sharing = original quality; file attachments degrade it.</t>
+        </is>
+      </c>
+      <c r="C327" s="31" t="n"/>
+      <c r="D327" s="31" t="n"/>
+      <c r="E327" s="31" t="n"/>
+      <c r="F327" s="31" t="n"/>
+    </row>
+    <row r="328" ht="24" customHeight="1">
+      <c r="A328" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B328" s="30" t="inlineStr">
+        <is>
+          <t>Works the same for PDFs, PPTs, and videos anywhere in the library.</t>
+        </is>
+      </c>
+      <c r="C328" s="31" t="n"/>
+      <c r="D328" s="31" t="n"/>
+      <c r="E328" s="31" t="n"/>
+      <c r="F328" s="31" t="n"/>
+    </row>
+    <row r="329" ht="26" customHeight="1">
+      <c r="A329" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Anyone with the link can open it. For internal-only material, check who you share with.</t>
+        </is>
+      </c>
+      <c r="B329" s="35" t="n"/>
+      <c r="C329" s="35" t="n"/>
+      <c r="D329" s="35" t="n"/>
+      <c r="E329" s="35" t="n"/>
+      <c r="F329" s="35" t="n"/>
+    </row>
+    <row r="330" ht="30" customHeight="1">
+      <c r="A330" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · In a parents' group chat, one video-guide link does all the explaining.</t>
+        </is>
+      </c>
+      <c r="B330" s="33" t="n"/>
+      <c r="C330" s="33" t="n"/>
+      <c r="D330" s="33" t="n"/>
+      <c r="E330" s="33" t="n"/>
+      <c r="F330" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="251">
+  <mergeCells count="300">
     <mergeCell ref="B106:F106"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B129:F129"/>
@@ -5031,6 +5760,7 @@
     <mergeCell ref="A189:F189"/>
     <mergeCell ref="B261:F261"/>
     <mergeCell ref="A158:F158"/>
+    <mergeCell ref="B292:F292"/>
     <mergeCell ref="B122:F122"/>
     <mergeCell ref="B184:F184"/>
     <mergeCell ref="A3:F3"/>
@@ -5039,23 +5769,31 @@
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B27:F27"/>
+    <mergeCell ref="A301:F301"/>
     <mergeCell ref="B52:F52"/>
     <mergeCell ref="B180:F180"/>
     <mergeCell ref="B223:F223"/>
     <mergeCell ref="B238:F238"/>
+    <mergeCell ref="B294:F294"/>
+    <mergeCell ref="B307:F307"/>
+    <mergeCell ref="B303:F303"/>
     <mergeCell ref="B195:F195"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B253:F253"/>
+    <mergeCell ref="A321:F321"/>
     <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A290:F290"/>
     <mergeCell ref="B170:F170"/>
     <mergeCell ref="A200:F200"/>
     <mergeCell ref="B250:F250"/>
+    <mergeCell ref="B328:F328"/>
     <mergeCell ref="A81:F81"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="A265:F265"/>
     <mergeCell ref="B234:F234"/>
+    <mergeCell ref="A288:F288"/>
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B270:F270"/>
@@ -5063,21 +5801,27 @@
     <mergeCell ref="B108:F108"/>
     <mergeCell ref="B186:F186"/>
     <mergeCell ref="A258:F258"/>
+    <mergeCell ref="A329:F329"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="B118:F118"/>
     <mergeCell ref="B143:F143"/>
     <mergeCell ref="A257:F257"/>
     <mergeCell ref="B30:F30"/>
+    <mergeCell ref="A291:F291"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="A60:F60"/>
+    <mergeCell ref="B281:F281"/>
     <mergeCell ref="B20:F20"/>
     <mergeCell ref="B133:F133"/>
     <mergeCell ref="B142:F142"/>
     <mergeCell ref="A70:F70"/>
     <mergeCell ref="B213:F213"/>
     <mergeCell ref="A241:F241"/>
+    <mergeCell ref="B313:F313"/>
     <mergeCell ref="B160:F160"/>
+    <mergeCell ref="B305:F305"/>
     <mergeCell ref="A124:F124"/>
+    <mergeCell ref="B306:F306"/>
     <mergeCell ref="B144:F144"/>
     <mergeCell ref="B233:F233"/>
     <mergeCell ref="B227:F227"/>
@@ -5095,13 +5839,17 @@
     <mergeCell ref="B105:F105"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B228:F228"/>
+    <mergeCell ref="A278:F278"/>
     <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B293:F293"/>
     <mergeCell ref="B120:F120"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="A254:F254"/>
+    <mergeCell ref="A311:F311"/>
     <mergeCell ref="A135:F135"/>
     <mergeCell ref="B107:F107"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B318:F318"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B175:F175"/>
     <mergeCell ref="B88:F88"/>
@@ -5111,7 +5859,9 @@
     <mergeCell ref="A199:F199"/>
     <mergeCell ref="B171:F171"/>
     <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B308:F308"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B317:F317"/>
     <mergeCell ref="A127:F127"/>
     <mergeCell ref="B99:F99"/>
     <mergeCell ref="A48:F48"/>
@@ -5122,7 +5872,9 @@
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B304:F304"/>
     <mergeCell ref="B239:F239"/>
+    <mergeCell ref="A319:F319"/>
     <mergeCell ref="B153:F153"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A178:F178"/>
@@ -5132,15 +5884,18 @@
     <mergeCell ref="B204:F204"/>
     <mergeCell ref="B216:F216"/>
     <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B296:F296"/>
     <mergeCell ref="B173:F173"/>
     <mergeCell ref="B271:F271"/>
     <mergeCell ref="B75:F75"/>
     <mergeCell ref="A137:F137"/>
     <mergeCell ref="B109:F109"/>
     <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B280:F280"/>
     <mergeCell ref="B62:F62"/>
     <mergeCell ref="A268:F268"/>
     <mergeCell ref="A217:F217"/>
+    <mergeCell ref="A330:F330"/>
     <mergeCell ref="B141:F141"/>
     <mergeCell ref="B193:F193"/>
     <mergeCell ref="B150:F150"/>
@@ -5150,8 +5905,11 @@
     <mergeCell ref="B215:F215"/>
     <mergeCell ref="B273:F273"/>
     <mergeCell ref="A26:F26"/>
+    <mergeCell ref="B282:F282"/>
     <mergeCell ref="A210:F210"/>
+    <mergeCell ref="B295:F295"/>
     <mergeCell ref="A179:F179"/>
+    <mergeCell ref="B325:F325"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="A71:F71"/>
     <mergeCell ref="A242:F242"/>
@@ -5159,9 +5917,12 @@
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B152:F152"/>
     <mergeCell ref="B272:F272"/>
+    <mergeCell ref="A322:F322"/>
     <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B323:F323"/>
     <mergeCell ref="A116:F116"/>
     <mergeCell ref="B259:F259"/>
+    <mergeCell ref="A309:F309"/>
     <mergeCell ref="A244:F244"/>
     <mergeCell ref="B181:F181"/>
     <mergeCell ref="B225:F225"/>
@@ -5170,6 +5931,7 @@
     <mergeCell ref="B191:F191"/>
     <mergeCell ref="B73:F73"/>
     <mergeCell ref="B249:F249"/>
+    <mergeCell ref="A299:F299"/>
     <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A68:F68"/>
@@ -5182,10 +5944,12 @@
     <mergeCell ref="A276:F276"/>
     <mergeCell ref="B260:F260"/>
     <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A279:F279"/>
     <mergeCell ref="B183:F183"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B324:F324"/>
     <mergeCell ref="B201:F201"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="B139:F139"/>
@@ -5197,7 +5961,9 @@
     <mergeCell ref="A103:F103"/>
     <mergeCell ref="B222:F222"/>
     <mergeCell ref="A168:F168"/>
+    <mergeCell ref="B284:F284"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="A287:F287"/>
     <mergeCell ref="B123:F123"/>
     <mergeCell ref="B154:F154"/>
     <mergeCell ref="B212:F212"/>
@@ -5207,8 +5973,10 @@
     <mergeCell ref="B110:F110"/>
     <mergeCell ref="B203:F203"/>
     <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B286:F286"/>
     <mergeCell ref="A128:F128"/>
     <mergeCell ref="B100:F100"/>
+    <mergeCell ref="B327:F327"/>
     <mergeCell ref="A255:F255"/>
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
@@ -5219,12 +5987,14 @@
     <mergeCell ref="B140:F140"/>
     <mergeCell ref="B155:F155"/>
     <mergeCell ref="B264:F264"/>
+    <mergeCell ref="B326:F326"/>
     <mergeCell ref="A104:F104"/>
     <mergeCell ref="B247:F247"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="B130:F130"/>
     <mergeCell ref="B77:F77"/>
+    <mergeCell ref="A302:F302"/>
     <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="B248:F248"/>
@@ -5235,6 +6005,8 @@
     <mergeCell ref="B235:F235"/>
     <mergeCell ref="B240:F240"/>
     <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B297:F297"/>
+    <mergeCell ref="A312:F312"/>
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B132:F132"/>
@@ -5249,12 +6021,17 @@
     <mergeCell ref="B78:F78"/>
     <mergeCell ref="B112:F112"/>
     <mergeCell ref="B205:F205"/>
+    <mergeCell ref="B283:F283"/>
+    <mergeCell ref="B314:F314"/>
     <mergeCell ref="A220:F220"/>
     <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B298:F298"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="B211:F211"/>
     <mergeCell ref="A275:F275"/>
+    <mergeCell ref="B285:F285"/>
+    <mergeCell ref="B316:F316"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B64:F64"/>
     <mergeCell ref="B95:F95"/>
@@ -5264,6 +6041,7 @@
     <mergeCell ref="A197:F197"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="A146:F146"/>
+    <mergeCell ref="B315:F315"/>
     <mergeCell ref="B79:F79"/>
     <mergeCell ref="B32:F32"/>
     <mergeCell ref="A187:F187"/>

--- a/cloudflare-deploy/public/library/admin/admin-en.xlsx
+++ b/cloudflare-deploy/public/library/admin/admin-en.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2078,168 @@
       <c r="E33" s="20" t="inlineStr">
         <is>
           <t>In a parents' group chat, one video-guide link does all the explaining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>💳</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Enrolment &amp; payment → automatic lesson creation</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Send students and parents the enrolment link. → They choose teacher → lesson options (weekly count, term, length) → days &amp; time. → The slot check must pass before the pay button unlocks (payment is blocked on a clash). → On confirmed payment, all sessions are created at once — verify in the admin lesson list. → Head-office prices and discount rates are managed on the pricing screen.</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>Consultation → level test → send the enrolment link is the smoothest conversion path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>👀</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Class Observation (live)</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Open the Class Observation (Live) card in the admin menu. → Enter your admin UID and the room ID. → Write an observation reason — this is required (e.g. new-teacher mentoring). → Press Start observing; press Stop observing when done. → Past sessions are listed under Observation log.</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>Observe new teachers once a week for their first two weeks, then coach — quality stabilises quickly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="54" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>🧭</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>A refreshed admin screen</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Press ‹ Collapse at the top of the left menu — it shrinks to an icon rail and the content gets wider. → Press the › button in the same place to expand it again. → The collapsed state is remembered for your next visit. → Too many menus to find one? Type its name into menu search at the top.</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>Wide-table screens like settlement and payroll are far easier to read with the menu collapsed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="54" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>🌐</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>The interface language sets itself</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>If the account has a nationality on file, the right language appears automatically at login. → To change it manually, press the 🌐 EN / KR button at the top. → A manual choice is stored per account — several people can share one PC without interference. → Teacher guide slides and manuals switch to the English editions with it.</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>Enter nationality when registering a new teacher and their very first login is in English — fewer support requests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="54" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Running Judgment Training (student judgment index)</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>The feature lives at AI Learning Tools → Judgment Training on the student screen. → Per-student results appear on the My Growth screen and in learning reports. → Show the index trend chart as supporting evidence during consultations.</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>This is the best material to answer the classic parent question: “They know the words but can't speak.”</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="54" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>🔑</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Teacher accounts (password reset · access limits)</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Find the teacher under Teachers in the admin menu. → Use Reset password to issue a temporary password. → Pass it on and tell them to change it right after logging in. → If the teacher's nationality is blank, fill it in so their screen opens in English.</t>
+        </is>
+      </c>
+      <c r="E39" s="20" t="inlineStr">
+        <is>
+          <t>Fill in nationality and contact details when registering a new teacher — later questions drop sharply.</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F330"/>
+  <dimension ref="A1:F408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5747,306 +5909,1264 @@
       <c r="E330" s="33" t="n"/>
       <c r="F330" s="33" t="n"/>
     </row>
+    <row r="332" ht="26" customHeight="1">
+      <c r="A332" s="21" t="inlineStr">
+        <is>
+          <t>31  💳 Enrolment &amp; payment → automatic lesson creation  —  Once payment is confirmed, every session is scheduled</t>
+        </is>
+      </c>
+      <c r="B332" s="22" t="n"/>
+      <c r="C332" s="22" t="n"/>
+      <c r="D332" s="22" t="n"/>
+      <c r="E332" s="22" t="n"/>
+      <c r="F332" s="22" t="n"/>
+    </row>
+    <row r="333" ht="42" customHeight="1">
+      <c r="A333" s="23" t="inlineStr">
+        <is>
+          <t>📖 On the Enrolment screen a student picks teacher, days and time and pays — and all lesson sessions are created automatically the moment payment is confirmed. The old manual timetable entry after payment is gone. If the slot clashes with an existing lesson, the conflict is detected before payment.</t>
+        </is>
+      </c>
+      <c r="B333" s="24" t="n"/>
+      <c r="C333" s="24" t="n"/>
+      <c r="D333" s="24" t="n"/>
+      <c r="E333" s="24" t="n"/>
+      <c r="F333" s="24" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B334" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="30" customHeight="1">
+      <c r="A335" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B335" s="28" t="inlineStr">
+        <is>
+          <t>Send students and parents the enrolment link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="30" customHeight="1">
+      <c r="A336" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B336" s="28" t="inlineStr">
+        <is>
+          <t>They choose teacher → lesson options (weekly count, term, length) → days &amp; time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="30" customHeight="1">
+      <c r="A337" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B337" s="28" t="inlineStr">
+        <is>
+          <t>The slot check must pass before the pay button unlocks (payment is blocked on a clash).</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="30" customHeight="1">
+      <c r="A338" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B338" s="28" t="inlineStr">
+        <is>
+          <t>On confirmed payment, all sessions are created at once — verify in the admin lesson list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="30" customHeight="1">
+      <c r="A339" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B339" s="28" t="inlineStr">
+        <is>
+          <t>Head-office prices and discount rates are managed on the pricing screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="24" customHeight="1">
+      <c r="A340" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B340" s="30" t="inlineStr">
+        <is>
+          <t>Idempotent — a duplicated payment callback will not create the sessions twice.</t>
+        </is>
+      </c>
+      <c r="C340" s="31" t="n"/>
+      <c r="D340" s="31" t="n"/>
+      <c r="E340" s="31" t="n"/>
+      <c r="F340" s="31" t="n"/>
+    </row>
+    <row r="341" ht="24" customHeight="1">
+      <c r="A341" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B341" s="30" t="inlineStr">
+        <is>
+          <t>Clashes with holidays or existing lessons are pushed back so the session count is still met.</t>
+        </is>
+      </c>
+      <c r="C341" s="31" t="n"/>
+      <c r="D341" s="31" t="n"/>
+      <c r="E341" s="31" t="n"/>
+      <c r="F341" s="31" t="n"/>
+    </row>
+    <row r="342" ht="24" customHeight="1">
+      <c r="A342" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B342" s="30" t="inlineStr">
+        <is>
+          <t>Term discounts (6 months −5%, 12 months −10%) are applied to the amount automatically.</t>
+        </is>
+      </c>
+      <c r="C342" s="31" t="n"/>
+      <c r="D342" s="31" t="n"/>
+      <c r="E342" s="31" t="n"/>
+      <c r="F342" s="31" t="n"/>
+    </row>
+    <row r="343" ht="26" customHeight="1">
+      <c r="A343" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Stage 1 (enrol → pay → auto-create sessions) is live today. Later stages will follow.</t>
+        </is>
+      </c>
+      <c r="B343" s="35" t="n"/>
+      <c r="C343" s="35" t="n"/>
+      <c r="D343" s="35" t="n"/>
+      <c r="E343" s="35" t="n"/>
+      <c r="F343" s="35" t="n"/>
+    </row>
+    <row r="344" ht="30" customHeight="1">
+      <c r="A344" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Consultation → level test → send the enrolment link is the smoothest conversion path.</t>
+        </is>
+      </c>
+      <c r="B344" s="33" t="n"/>
+      <c r="C344" s="33" t="n"/>
+      <c r="D344" s="33" t="n"/>
+      <c r="E344" s="33" t="n"/>
+      <c r="F344" s="33" t="n"/>
+    </row>
+    <row r="346" ht="26" customHeight="1">
+      <c r="A346" s="21" t="inlineStr">
+        <is>
+          <t>32  👀 Class Observation (live)  —  Quietly look in on a lesson in progress</t>
+        </is>
+      </c>
+      <c r="B346" s="22" t="n"/>
+      <c r="C346" s="22" t="n"/>
+      <c r="D346" s="22" t="n"/>
+      <c r="E346" s="22" t="n"/>
+      <c r="F346" s="22" t="n"/>
+    </row>
+    <row r="347" ht="42" customHeight="1">
+      <c r="A347" s="23" t="inlineStr">
+        <is>
+          <t>📖 You can sit in on a live lesson without the student or teacher knowing. No join notification is sent, so the lesson isn't disturbed — use it for mentoring new teachers, quality checks and parent complaints. Every observation is permanently written to the audit log.</t>
+        </is>
+      </c>
+      <c r="B347" s="24" t="n"/>
+      <c r="C347" s="24" t="n"/>
+      <c r="D347" s="24" t="n"/>
+      <c r="E347" s="24" t="n"/>
+      <c r="F347" s="24" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B348" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="30" customHeight="1">
+      <c r="A349" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B349" s="28" t="inlineStr">
+        <is>
+          <t>Open the Class Observation (Live) card in the admin menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="30" customHeight="1">
+      <c r="A350" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B350" s="28" t="inlineStr">
+        <is>
+          <t>Enter your admin UID and the room ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="30" customHeight="1">
+      <c r="A351" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B351" s="28" t="inlineStr">
+        <is>
+          <t>Write an observation reason — this is required (e.g. new-teacher mentoring).</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="30" customHeight="1">
+      <c r="A352" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B352" s="28" t="inlineStr">
+        <is>
+          <t>Press Start observing; press Stop observing when done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="30" customHeight="1">
+      <c r="A353" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B353" s="28" t="inlineStr">
+        <is>
+          <t>Past sessions are listed under Observation log.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="24" customHeight="1">
+      <c r="A354" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B354" s="30" t="inlineStr">
+        <is>
+          <t>While observing, your audio and video are not transmitted.</t>
+        </is>
+      </c>
+      <c r="C354" s="31" t="n"/>
+      <c r="D354" s="31" t="n"/>
+      <c r="E354" s="31" t="n"/>
+      <c r="F354" s="31" t="n"/>
+    </row>
+    <row r="355" ht="24" customHeight="1">
+      <c r="A355" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B355" s="30" t="inlineStr">
+        <is>
+          <t>A reason is mandatory — this is student privacy policy.</t>
+        </is>
+      </c>
+      <c r="C355" s="31" t="n"/>
+      <c r="D355" s="31" t="n"/>
+      <c r="E355" s="31" t="n"/>
+      <c r="F355" s="31" t="n"/>
+    </row>
+    <row r="356" ht="24" customHeight="1">
+      <c r="A356" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B356" s="30" t="inlineStr">
+        <is>
+          <t>Who observed, when and why is fully recorded.</t>
+        </is>
+      </c>
+      <c r="C356" s="31" t="n"/>
+      <c r="D356" s="31" t="n"/>
+      <c r="E356" s="31" t="n"/>
+      <c r="F356" s="31" t="n"/>
+    </row>
+    <row r="357" ht="26" customHeight="1">
+      <c r="A357" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · This touches student privacy directly. Use it only when there is a business need, and write a specific reason.</t>
+        </is>
+      </c>
+      <c r="B357" s="35" t="n"/>
+      <c r="C357" s="35" t="n"/>
+      <c r="D357" s="35" t="n"/>
+      <c r="E357" s="35" t="n"/>
+      <c r="F357" s="35" t="n"/>
+    </row>
+    <row r="358" ht="30" customHeight="1">
+      <c r="A358" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Observe new teachers once a week for their first two weeks, then coach — quality stabilises quickly.</t>
+        </is>
+      </c>
+      <c r="B358" s="33" t="n"/>
+      <c r="C358" s="33" t="n"/>
+      <c r="D358" s="33" t="n"/>
+      <c r="E358" s="33" t="n"/>
+      <c r="F358" s="33" t="n"/>
+    </row>
+    <row r="360" ht="26" customHeight="1">
+      <c r="A360" s="21" t="inlineStr">
+        <is>
+          <t>33  🧭 A refreshed admin screen  —  Collapsible sidebar · lighter background · line icons</t>
+        </is>
+      </c>
+      <c r="B360" s="22" t="n"/>
+      <c r="C360" s="22" t="n"/>
+      <c r="D360" s="22" t="n"/>
+      <c r="E360" s="22" t="n"/>
+      <c r="F360" s="22" t="n"/>
+    </row>
+    <row r="361" ht="42" customHeight="1">
+      <c r="A361" s="23" t="inlineStr">
+        <is>
+          <t>📖 The admin screen is now easier on the eyes and wider. The left menu collapses to a narrow icon rail via the ‹ Collapse button, and the background is now a consistent light tone. Menu icons were redrawn as line icons so labels read clearly.</t>
+        </is>
+      </c>
+      <c r="B361" s="24" t="n"/>
+      <c r="C361" s="24" t="n"/>
+      <c r="D361" s="24" t="n"/>
+      <c r="E361" s="24" t="n"/>
+      <c r="F361" s="24" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B362" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="30" customHeight="1">
+      <c r="A363" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B363" s="28" t="inlineStr">
+        <is>
+          <t>Press ‹ Collapse at the top of the left menu — it shrinks to an icon rail and the content gets wider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="30" customHeight="1">
+      <c r="A364" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B364" s="28" t="inlineStr">
+        <is>
+          <t>Press the › button in the same place to expand it again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="30" customHeight="1">
+      <c r="A365" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B365" s="28" t="inlineStr">
+        <is>
+          <t>The collapsed state is remembered for your next visit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="30" customHeight="1">
+      <c r="A366" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B366" s="28" t="inlineStr">
+        <is>
+          <t>Too many menus to find one? Type its name into menu search at the top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="24" customHeight="1">
+      <c r="A367" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B367" s="30" t="inlineStr">
+        <is>
+          <t>Screens full of tables and lists gain a lot of horizontal space.</t>
+        </is>
+      </c>
+      <c r="C367" s="31" t="n"/>
+      <c r="D367" s="31" t="n"/>
+      <c r="E367" s="31" t="n"/>
+      <c r="F367" s="31" t="n"/>
+    </row>
+    <row r="368" ht="24" customHeight="1">
+      <c r="A368" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B368" s="30" t="inlineStr">
+        <is>
+          <t>15 sub-pages were moved onto the same light theme, so the colour jump between screens is gone.</t>
+        </is>
+      </c>
+      <c r="C368" s="31" t="n"/>
+      <c r="D368" s="31" t="n"/>
+      <c r="E368" s="31" t="n"/>
+      <c r="F368" s="31" t="n"/>
+    </row>
+    <row r="369" ht="24" customHeight="1">
+      <c r="A369" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B369" s="30" t="inlineStr">
+        <is>
+          <t>The collapse animation was removed so low-spec PCs don't stutter.</t>
+        </is>
+      </c>
+      <c r="C369" s="31" t="n"/>
+      <c r="D369" s="31" t="n"/>
+      <c r="E369" s="31" t="n"/>
+      <c r="F369" s="31" t="n"/>
+    </row>
+    <row r="370" ht="30" customHeight="1">
+      <c r="A370" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Wide-table screens like settlement and payroll are far easier to read with the menu collapsed.</t>
+        </is>
+      </c>
+      <c r="B370" s="33" t="n"/>
+      <c r="C370" s="33" t="n"/>
+      <c r="D370" s="33" t="n"/>
+      <c r="E370" s="33" t="n"/>
+      <c r="F370" s="33" t="n"/>
+    </row>
+    <row r="372" ht="26" customHeight="1">
+      <c r="A372" s="21" t="inlineStr">
+        <is>
+          <t>34  🌐 The interface language sets itself  —  Overseas staff and teachers start in English</t>
+        </is>
+      </c>
+      <c r="B372" s="22" t="n"/>
+      <c r="C372" s="22" t="n"/>
+      <c r="D372" s="22" t="n"/>
+      <c r="E372" s="22" t="n"/>
+      <c r="F372" s="22" t="n"/>
+    </row>
+    <row r="373" ht="42" customHeight="1">
+      <c r="A373" s="23" t="inlineStr">
+        <is>
+          <t>📖 Filipino teachers and overseas staff now start in English from the first screen. The interface language is decided from the account's nationality, and teacher accounts are always English regardless of name or previous choice. You can still switch any time with the 🌐 EN / KR button at the top.</t>
+        </is>
+      </c>
+      <c r="B373" s="24" t="n"/>
+      <c r="C373" s="24" t="n"/>
+      <c r="D373" s="24" t="n"/>
+      <c r="E373" s="24" t="n"/>
+      <c r="F373" s="24" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B374" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="30" customHeight="1">
+      <c r="A375" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B375" s="28" t="inlineStr">
+        <is>
+          <t>If the account has a nationality on file, the right language appears automatically at login.</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="30" customHeight="1">
+      <c r="A376" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B376" s="28" t="inlineStr">
+        <is>
+          <t>To change it manually, press the 🌐 EN / KR button at the top.</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="30" customHeight="1">
+      <c r="A377" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B377" s="28" t="inlineStr">
+        <is>
+          <t>A manual choice is stored per account — several people can share one PC without interference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="30" customHeight="1">
+      <c r="A378" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B378" s="28" t="inlineStr">
+        <is>
+          <t>Teacher guide slides and manuals switch to the English editions with it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="24" customHeight="1">
+      <c r="A379" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B379" s="30" t="inlineStr">
+        <is>
+          <t>Teacher accounts are always English — no more getting lost in a Korean screen.</t>
+        </is>
+      </c>
+      <c r="C379" s="31" t="n"/>
+      <c r="D379" s="31" t="n"/>
+      <c r="E379" s="31" t="n"/>
+      <c r="F379" s="31" t="n"/>
+    </row>
+    <row r="380" ht="24" customHeight="1">
+      <c r="A380" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B380" s="30" t="inlineStr">
+        <is>
+          <t>Accounts with an English name no longer flip to Korean because of a Korean job title.</t>
+        </is>
+      </c>
+      <c r="C380" s="31" t="n"/>
+      <c r="D380" s="31" t="n"/>
+      <c r="E380" s="31" t="n"/>
+      <c r="F380" s="31" t="n"/>
+    </row>
+    <row r="381" ht="24" customHeight="1">
+      <c r="A381" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B381" s="30" t="inlineStr">
+        <is>
+          <t>Language choice is isolated per account, so an overseas account isn't overwritten by someone else's pick.</t>
+        </is>
+      </c>
+      <c r="C381" s="31" t="n"/>
+      <c r="D381" s="31" t="n"/>
+      <c r="E381" s="31" t="n"/>
+      <c r="F381" s="31" t="n"/>
+    </row>
+    <row r="382" ht="26" customHeight="1">
+      <c r="A382" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Accounts with no nationality fall back to the old name/ID heuristic. Please fill in nationality when registering teachers.</t>
+        </is>
+      </c>
+      <c r="B382" s="35" t="n"/>
+      <c r="C382" s="35" t="n"/>
+      <c r="D382" s="35" t="n"/>
+      <c r="E382" s="35" t="n"/>
+      <c r="F382" s="35" t="n"/>
+    </row>
+    <row r="383" ht="30" customHeight="1">
+      <c r="A383" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Enter nationality when registering a new teacher and their very first login is in English — fewer support requests.</t>
+        </is>
+      </c>
+      <c r="B383" s="33" t="n"/>
+      <c r="C383" s="33" t="n"/>
+      <c r="D383" s="33" t="n"/>
+      <c r="E383" s="33" t="n"/>
+      <c r="F383" s="33" t="n"/>
+    </row>
+    <row r="385" ht="26" customHeight="1">
+      <c r="A385" s="21" t="inlineStr">
+        <is>
+          <t>35  🧠 Running Judgment Training (student judgment index)  —  Not memorisation but judgment — a new outcome metric</t>
+        </is>
+      </c>
+      <c r="B385" s="22" t="n"/>
+      <c r="C385" s="22" t="n"/>
+      <c r="D385" s="22" t="n"/>
+      <c r="E385" s="22" t="n"/>
+      <c r="F385" s="22" t="n"/>
+    </row>
+    <row r="386" ht="42" customHeight="1">
+      <c r="A386" s="23" t="inlineStr">
+        <is>
+          <t>📖 In Judgment Training, a student picks the expression that fits a situation and explains why. Results accumulate into a judgment index across 5 axes — evidence you can show in parent consultations that answers “how well do they judge for themselves”, not just “what did they memorise”.</t>
+        </is>
+      </c>
+      <c r="B386" s="24" t="n"/>
+      <c r="C386" s="24" t="n"/>
+      <c r="D386" s="24" t="n"/>
+      <c r="E386" s="24" t="n"/>
+      <c r="F386" s="24" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B387" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="30" customHeight="1">
+      <c r="A388" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B388" s="28" t="inlineStr">
+        <is>
+          <t>The feature lives at AI Learning Tools → Judgment Training on the student screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="30" customHeight="1">
+      <c r="A389" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B389" s="28" t="inlineStr">
+        <is>
+          <t>Per-student results appear on the My Growth screen and in learning reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="30" customHeight="1">
+      <c r="A390" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B390" s="28" t="inlineStr">
+        <is>
+          <t>Show the index trend chart as supporting evidence during consultations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="24" customHeight="1">
+      <c r="A391" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B391" s="30" t="inlineStr">
+        <is>
+          <t>Recent answers are weighted more (half-life weighting), so current ability shows up fast.</t>
+        </is>
+      </c>
+      <c r="C391" s="31" t="n"/>
+      <c r="D391" s="31" t="n"/>
+      <c r="E391" s="31" t="n"/>
+      <c r="F391" s="31" t="n"/>
+    </row>
+    <row r="392" ht="24" customHeight="1">
+      <c r="A392" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B392" s="30" t="inlineStr">
+        <is>
+          <t>Partial credit means one wrong answer doesn't crash the index.</t>
+        </is>
+      </c>
+      <c r="C392" s="31" t="n"/>
+      <c r="D392" s="31" t="n"/>
+      <c r="E392" s="31" t="n"/>
+      <c r="F392" s="31" t="n"/>
+    </row>
+    <row r="393" ht="24" customHeight="1">
+      <c r="A393" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B393" s="30" t="inlineStr">
+        <is>
+          <t>Questions combine 24 topics × 12 angles, so students get different questions.</t>
+        </is>
+      </c>
+      <c r="C393" s="31" t="n"/>
+      <c r="D393" s="31" t="n"/>
+      <c r="E393" s="31" t="n"/>
+      <c r="F393" s="31" t="n"/>
+    </row>
+    <row r="394" ht="26" customHeight="1">
+      <c r="A394" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Read the judgment index as a growth trend, not an exam score. The direction matters more than the absolute number.</t>
+        </is>
+      </c>
+      <c r="B394" s="35" t="n"/>
+      <c r="C394" s="35" t="n"/>
+      <c r="D394" s="35" t="n"/>
+      <c r="E394" s="35" t="n"/>
+      <c r="F394" s="35" t="n"/>
+    </row>
+    <row r="395" ht="30" customHeight="1">
+      <c r="A395" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · This is the best material to answer the classic parent question: “They know the words but can't speak.”</t>
+        </is>
+      </c>
+      <c r="B395" s="33" t="n"/>
+      <c r="C395" s="33" t="n"/>
+      <c r="D395" s="33" t="n"/>
+      <c r="E395" s="33" t="n"/>
+      <c r="F395" s="33" t="n"/>
+    </row>
+    <row r="397" ht="26" customHeight="1">
+      <c r="A397" s="21" t="inlineStr">
+        <is>
+          <t>36  🔑 Teacher accounts (password reset · access limits)  —  Handling lost passwords · scoping permissions</t>
+        </is>
+      </c>
+      <c r="B397" s="22" t="n"/>
+      <c r="C397" s="22" t="n"/>
+      <c r="D397" s="22" t="n"/>
+      <c r="E397" s="22" t="n"/>
+      <c r="F397" s="22" t="n"/>
+    </row>
+    <row r="398" ht="42" customHeight="1">
+      <c r="A398" s="23" t="inlineStr">
+        <is>
+          <t>📖 When a teacher forgets their password you can reset it directly from the admin screen. Teacher account access was also tightened so that operations and settlement features a teacher doesn't need simply don't open.</t>
+        </is>
+      </c>
+      <c r="B398" s="24" t="n"/>
+      <c r="C398" s="24" t="n"/>
+      <c r="D398" s="24" t="n"/>
+      <c r="E398" s="24" t="n"/>
+      <c r="F398" s="24" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="25" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B399" s="26" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="30" customHeight="1">
+      <c r="A400" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B400" s="28" t="inlineStr">
+        <is>
+          <t>Find the teacher under Teachers in the admin menu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="30" customHeight="1">
+      <c r="A401" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B401" s="28" t="inlineStr">
+        <is>
+          <t>Use Reset password to issue a temporary password.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="30" customHeight="1">
+      <c r="A402" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B402" s="28" t="inlineStr">
+        <is>
+          <t>Pass it on and tell them to change it right after logging in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="30" customHeight="1">
+      <c r="A403" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="B403" s="28" t="inlineStr">
+        <is>
+          <t>If the teacher's nationality is blank, fill it in so their screen opens in English.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="24" customHeight="1">
+      <c r="A404" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B404" s="30" t="inlineStr">
+        <is>
+          <t>Teacher accounts cannot reach operations or settlement features (32 areas blocked).</t>
+        </is>
+      </c>
+      <c r="C404" s="31" t="n"/>
+      <c r="D404" s="31" t="n"/>
+      <c r="E404" s="31" t="n"/>
+      <c r="F404" s="31" t="n"/>
+    </row>
+    <row r="405" ht="24" customHeight="1">
+      <c r="A405" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B405" s="30" t="inlineStr">
+        <is>
+          <t>Reset actions are logged.</t>
+        </is>
+      </c>
+      <c r="C405" s="31" t="n"/>
+      <c r="D405" s="31" t="n"/>
+      <c r="E405" s="31" t="n"/>
+      <c r="F405" s="31" t="n"/>
+    </row>
+    <row r="406" ht="24" customHeight="1">
+      <c r="A406" s="29" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="B406" s="30" t="inlineStr">
+        <is>
+          <t>Teachers with a nationality on file start in English from their first login.</t>
+        </is>
+      </c>
+      <c r="C406" s="31" t="n"/>
+      <c r="D406" s="31" t="n"/>
+      <c r="E406" s="31" t="n"/>
+      <c r="F406" s="31" t="n"/>
+    </row>
+    <row r="407" ht="26" customHeight="1">
+      <c r="A407" s="34" t="inlineStr">
+        <is>
+          <t>⚠️ Good to know · Send temporary passwords only over a channel where you can verify who you're talking to.</t>
+        </is>
+      </c>
+      <c r="B407" s="35" t="n"/>
+      <c r="C407" s="35" t="n"/>
+      <c r="D407" s="35" t="n"/>
+      <c r="E407" s="35" t="n"/>
+      <c r="F407" s="35" t="n"/>
+    </row>
+    <row r="408" ht="30" customHeight="1">
+      <c r="A408" s="32" t="inlineStr">
+        <is>
+          <t>💡 Tip · Fill in nationality and contact details when registering a new teacher — later questions drop sharply.</t>
+        </is>
+      </c>
+      <c r="B408" s="33" t="n"/>
+      <c r="C408" s="33" t="n"/>
+      <c r="D408" s="33" t="n"/>
+      <c r="E408" s="33" t="n"/>
+      <c r="F408" s="33" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="300">
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="A84:F84"/>
+  <mergeCells count="372">
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B194:F194"/>
-    <mergeCell ref="B252:F252"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="A189:F189"/>
-    <mergeCell ref="B261:F261"/>
-    <mergeCell ref="A158:F158"/>
-    <mergeCell ref="B292:F292"/>
+    <mergeCell ref="A394:F394"/>
     <mergeCell ref="B122:F122"/>
-    <mergeCell ref="B184:F184"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B236:F236"/>
     <mergeCell ref="B214:F214"/>
     <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="A301:F301"/>
-    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B238:F238"/>
+    <mergeCell ref="B303:F303"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B253:F253"/>
+    <mergeCell ref="B342:F342"/>
+    <mergeCell ref="A372:F372"/>
+    <mergeCell ref="A347:F347"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A257:F257"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B369:F369"/>
+    <mergeCell ref="B356:F356"/>
+    <mergeCell ref="B160:F160"/>
+    <mergeCell ref="B368:F368"/>
+    <mergeCell ref="B306:F306"/>
+    <mergeCell ref="B233:F233"/>
+    <mergeCell ref="B227:F227"/>
+    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="B72:F72"/>
+    <mergeCell ref="A267:F267"/>
+    <mergeCell ref="B228:F228"/>
+    <mergeCell ref="B293:F293"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A333:F333"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="A199:F199"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B317:F317"/>
+    <mergeCell ref="B388:F388"/>
+    <mergeCell ref="B304:F304"/>
+    <mergeCell ref="B375:F375"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="A346:F346"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="B141:F141"/>
+    <mergeCell ref="B401:F401"/>
+    <mergeCell ref="B272:F272"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B259:F259"/>
+    <mergeCell ref="B225:F225"/>
+    <mergeCell ref="B274:F274"/>
+    <mergeCell ref="B249:F249"/>
+    <mergeCell ref="B363:F363"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A276:F276"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A383:F383"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A370:F370"/>
+    <mergeCell ref="B325:F325"/>
+    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="B390:F390"/>
+    <mergeCell ref="B389:F389"/>
+    <mergeCell ref="B327:F327"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B264:F264"/>
+    <mergeCell ref="B391:F391"/>
+    <mergeCell ref="B247:F247"/>
+    <mergeCell ref="A302:F302"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B262:F262"/>
+    <mergeCell ref="B151:F151"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A156:F156"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="A220:F220"/>
+    <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B211:F211"/>
+    <mergeCell ref="B338:F338"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="B340:F340"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B315:F315"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B404:F404"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="B252:F252"/>
+    <mergeCell ref="B366:F366"/>
     <mergeCell ref="B180:F180"/>
-    <mergeCell ref="B223:F223"/>
-    <mergeCell ref="B238:F238"/>
-    <mergeCell ref="B294:F294"/>
-    <mergeCell ref="B307:F307"/>
-    <mergeCell ref="B303:F303"/>
-    <mergeCell ref="B195:F195"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B253:F253"/>
+    <mergeCell ref="B381:F381"/>
     <mergeCell ref="A321:F321"/>
-    <mergeCell ref="A159:F159"/>
-    <mergeCell ref="A290:F290"/>
+    <mergeCell ref="A386:F386"/>
     <mergeCell ref="B170:F170"/>
-    <mergeCell ref="A200:F200"/>
-    <mergeCell ref="B250:F250"/>
+    <mergeCell ref="A373:F373"/>
     <mergeCell ref="B328:F328"/>
     <mergeCell ref="A81:F81"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="A265:F265"/>
     <mergeCell ref="B234:F234"/>
-    <mergeCell ref="A288:F288"/>
     <mergeCell ref="B172:F172"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B270:F270"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B392:F392"/>
     <mergeCell ref="B186:F186"/>
-    <mergeCell ref="A258:F258"/>
-    <mergeCell ref="A329:F329"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B143:F143"/>
-    <mergeCell ref="A257:F257"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="A291:F291"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="B281:F281"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B133:F133"/>
-    <mergeCell ref="B142:F142"/>
     <mergeCell ref="A70:F70"/>
-    <mergeCell ref="B213:F213"/>
     <mergeCell ref="A241:F241"/>
-    <mergeCell ref="B313:F313"/>
-    <mergeCell ref="B160:F160"/>
-    <mergeCell ref="B305:F305"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="B306:F306"/>
-    <mergeCell ref="B144:F144"/>
-    <mergeCell ref="B233:F233"/>
-    <mergeCell ref="B227:F227"/>
-    <mergeCell ref="B224:F224"/>
+    <mergeCell ref="A397:F397"/>
     <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B72:F72"/>
     <mergeCell ref="B185:F185"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="A267:F267"/>
-    <mergeCell ref="A149:F149"/>
-    <mergeCell ref="B121:F121"/>
     <mergeCell ref="A101:F101"/>
     <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B96:F96"/>
     <mergeCell ref="B105:F105"/>
     <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B228:F228"/>
-    <mergeCell ref="A278:F278"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="B293:F293"/>
+    <mergeCell ref="B341:F341"/>
     <mergeCell ref="B120:F120"/>
-    <mergeCell ref="B98:F98"/>
     <mergeCell ref="A254:F254"/>
     <mergeCell ref="A311:F311"/>
-    <mergeCell ref="A135:F135"/>
     <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B318:F318"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B175:F175"/>
-    <mergeCell ref="B88:F88"/>
+    <mergeCell ref="B405:F405"/>
     <mergeCell ref="A125:F125"/>
-    <mergeCell ref="A190:F190"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="A199:F199"/>
     <mergeCell ref="B171:F171"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B308:F308"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B317:F317"/>
     <mergeCell ref="A127:F127"/>
-    <mergeCell ref="B99:F99"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A176:F176"/>
-    <mergeCell ref="A232:F232"/>
     <mergeCell ref="A114:F114"/>
-    <mergeCell ref="B269:F269"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B304:F304"/>
-    <mergeCell ref="B239:F239"/>
-    <mergeCell ref="A319:F319"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="A169:F169"/>
     <mergeCell ref="A178:F178"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B251:F251"/>
-    <mergeCell ref="B76:F76"/>
     <mergeCell ref="B204:F204"/>
-    <mergeCell ref="B216:F216"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B296:F296"/>
     <mergeCell ref="B173:F173"/>
     <mergeCell ref="B271:F271"/>
     <mergeCell ref="B75:F75"/>
-    <mergeCell ref="A137:F137"/>
-    <mergeCell ref="B109:F109"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="B280:F280"/>
     <mergeCell ref="B62:F62"/>
-    <mergeCell ref="A268:F268"/>
-    <mergeCell ref="A217:F217"/>
-    <mergeCell ref="A330:F330"/>
-    <mergeCell ref="B141:F141"/>
-    <mergeCell ref="B193:F193"/>
-    <mergeCell ref="B150:F150"/>
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B202:F202"/>
+    <mergeCell ref="B273:F273"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A242:F242"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A244:F244"/>
+    <mergeCell ref="A231:F231"/>
+    <mergeCell ref="A407:F407"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B349:F349"/>
+    <mergeCell ref="A344:F344"/>
+    <mergeCell ref="A229:F229"/>
+    <mergeCell ref="B226:F226"/>
+    <mergeCell ref="A245:F245"/>
+    <mergeCell ref="B364:F364"/>
+    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B284:F284"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="B222:F222"/>
+    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B221:F221"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B286:F286"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A255:F255"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="B248:F248"/>
+    <mergeCell ref="A219:F219"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="B235:F235"/>
+    <mergeCell ref="B297:F297"/>
+    <mergeCell ref="B362:F362"/>
+    <mergeCell ref="B337:F337"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B205:F205"/>
+    <mergeCell ref="B339:F339"/>
+    <mergeCell ref="B314:F314"/>
+    <mergeCell ref="B376:F376"/>
+    <mergeCell ref="B403:F403"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="A408:F408"/>
+    <mergeCell ref="A187:F187"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B194:F194"/>
+    <mergeCell ref="B365:F365"/>
+    <mergeCell ref="B292:F292"/>
+    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B236:F236"/>
+    <mergeCell ref="B307:F307"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B223:F223"/>
+    <mergeCell ref="B294:F294"/>
+    <mergeCell ref="B350:F350"/>
+    <mergeCell ref="B195:F195"/>
+    <mergeCell ref="A200:F200"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="A265:F265"/>
+    <mergeCell ref="A357:F357"/>
+    <mergeCell ref="A258:F258"/>
+    <mergeCell ref="A329:F329"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A358:F358"/>
+    <mergeCell ref="B142:F142"/>
+    <mergeCell ref="B313:F313"/>
+    <mergeCell ref="B213:F213"/>
+    <mergeCell ref="B378:F378"/>
+    <mergeCell ref="B305:F305"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A360:F360"/>
+    <mergeCell ref="B144:F144"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A385:F385"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B318:F318"/>
+    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B308:F308"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A319:F319"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B239:F239"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B374:F374"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="A330:F330"/>
+    <mergeCell ref="A268:F268"/>
+    <mergeCell ref="B150:F150"/>
     <mergeCell ref="A145:F145"/>
     <mergeCell ref="B215:F215"/>
-    <mergeCell ref="B273:F273"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B263:F263"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B323:F323"/>
+    <mergeCell ref="A361:F361"/>
+    <mergeCell ref="B387:F387"/>
+    <mergeCell ref="B181:F181"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B260:F260"/>
+    <mergeCell ref="A279:F279"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A287:F287"/>
+    <mergeCell ref="A343:F343"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B334:F334"/>
+    <mergeCell ref="B380:F380"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="B165:F165"/>
+    <mergeCell ref="B336:F336"/>
+    <mergeCell ref="B140:F140"/>
+    <mergeCell ref="B400:F400"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B240:F240"/>
+    <mergeCell ref="B402:F402"/>
+    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="B377:F377"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A382:F382"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A275:F275"/>
+    <mergeCell ref="B316:F316"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B393:F393"/>
+    <mergeCell ref="A146:F146"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B324:F324"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B261:F261"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="B184:F184"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A301:F301"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A290:F290"/>
+    <mergeCell ref="A395:F395"/>
+    <mergeCell ref="B250:F250"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="A332:F332"/>
+    <mergeCell ref="A288:F288"/>
+    <mergeCell ref="B352:F352"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B143:F143"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B281:F281"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B355:F355"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B121:F121"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="A278:F278"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B98:F98"/>
+    <mergeCell ref="B175:F175"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B269:F269"/>
+    <mergeCell ref="A232:F232"/>
+    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="B251:F251"/>
+    <mergeCell ref="B216:F216"/>
+    <mergeCell ref="A398:F398"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="B280:F280"/>
+    <mergeCell ref="B351:F351"/>
+    <mergeCell ref="B193:F193"/>
+    <mergeCell ref="B295:F295"/>
     <mergeCell ref="B282:F282"/>
-    <mergeCell ref="A210:F210"/>
-    <mergeCell ref="B295:F295"/>
     <mergeCell ref="A179:F179"/>
-    <mergeCell ref="B325:F325"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A242:F242"/>
-    <mergeCell ref="B263:F263"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B272:F272"/>
     <mergeCell ref="A322:F322"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B323:F323"/>
     <mergeCell ref="A116:F116"/>
-    <mergeCell ref="B259:F259"/>
     <mergeCell ref="A309:F309"/>
-    <mergeCell ref="A244:F244"/>
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B225:F225"/>
-    <mergeCell ref="A231:F231"/>
-    <mergeCell ref="B274:F274"/>
-    <mergeCell ref="B191:F191"/>
     <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B249:F249"/>
     <mergeCell ref="A299:F299"/>
-    <mergeCell ref="B87:F87"/>
     <mergeCell ref="A93:F93"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A117:F117"/>
-    <mergeCell ref="A229:F229"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="B226:F226"/>
-    <mergeCell ref="A245:F245"/>
-    <mergeCell ref="A276:F276"/>
-    <mergeCell ref="B260:F260"/>
-    <mergeCell ref="A166:F166"/>
-    <mergeCell ref="A279:F279"/>
+    <mergeCell ref="B379:F379"/>
     <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B324:F324"/>
     <mergeCell ref="B201:F201"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="B335:F335"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B164:F164"/>
-    <mergeCell ref="A207:F207"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A103:F103"/>
-    <mergeCell ref="B222:F222"/>
-    <mergeCell ref="A168:F168"/>
-    <mergeCell ref="B284:F284"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="A287:F287"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B154:F154"/>
+    <mergeCell ref="B406:F406"/>
     <mergeCell ref="B212:F212"/>
     <mergeCell ref="B206:F206"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B399:F399"/>
     <mergeCell ref="B203:F203"/>
-    <mergeCell ref="B221:F221"/>
-    <mergeCell ref="B286:F286"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="B100:F100"/>
-    <mergeCell ref="B327:F327"/>
-    <mergeCell ref="A255:F255"/>
-    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="B165:F165"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B140:F140"/>
-    <mergeCell ref="B155:F155"/>
-    <mergeCell ref="B264:F264"/>
     <mergeCell ref="B326:F326"/>
     <mergeCell ref="A104:F104"/>
-    <mergeCell ref="B247:F247"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
     <mergeCell ref="B130:F130"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="A302:F302"/>
-    <mergeCell ref="B86:F86"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="B248:F248"/>
-    <mergeCell ref="B262:F262"/>
-    <mergeCell ref="A219:F219"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="B151:F151"/>
-    <mergeCell ref="B235:F235"/>
-    <mergeCell ref="B240:F240"/>
+    <mergeCell ref="A312:F312"/>
+    <mergeCell ref="B353:F353"/>
     <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B297:F297"/>
-    <mergeCell ref="A312:F312"/>
     <mergeCell ref="B61:F61"/>
-    <mergeCell ref="A4:F4"/>
     <mergeCell ref="B132:F132"/>
-    <mergeCell ref="A209:F209"/>
-    <mergeCell ref="A91:F91"/>
     <mergeCell ref="B119:F119"/>
-    <mergeCell ref="A156:F156"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B38:F38"/>
     <mergeCell ref="B196:F196"/>
-    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B367:F367"/>
     <mergeCell ref="B112:F112"/>
-    <mergeCell ref="B205:F205"/>
     <mergeCell ref="B283:F283"/>
-    <mergeCell ref="B314:F314"/>
-    <mergeCell ref="A220:F220"/>
-    <mergeCell ref="B246:F246"/>
+    <mergeCell ref="B354:F354"/>
+    <mergeCell ref="B348:F348"/>
     <mergeCell ref="B298:F298"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="A148:F148"/>
-    <mergeCell ref="B211:F211"/>
-    <mergeCell ref="A275:F275"/>
     <mergeCell ref="B285:F285"/>
-    <mergeCell ref="B316:F316"/>
-    <mergeCell ref="B55:F55"/>
     <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B89:F89"/>
     <mergeCell ref="A138:F138"/>
-    <mergeCell ref="A197:F197"/>
     <mergeCell ref="B51:F51"/>
-    <mergeCell ref="A146:F146"/>
-    <mergeCell ref="B315:F315"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="A187:F187"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B97:F97"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="B237:F237"/>
   </mergeCells>
